--- a/corrected-bank-specimens-for-user/02-nib/parsed-excel/NIB cash bk - parsed.xlsx
+++ b/corrected-bank-specimens-for-user/02-nib/parsed-excel/NIB cash bk - parsed.xlsx
@@ -428,7 +428,7 @@
         <v>Exported</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-07-08T16:17:00.957Z</v>
+        <v>2026-07-14T13:50:03.645Z</v>
       </c>
     </row>
     <row r="5">

--- a/corrected-bank-specimens-for-user/02-nib/parsed-excel/NIB cash bk - parsed.xlsx
+++ b/corrected-bank-specimens-for-user/02-nib/parsed-excel/NIB cash bk - parsed.xlsx
@@ -428,7 +428,7 @@
         <v>Exported</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-07-14T13:50:03.645Z</v>
+        <v>2026-07-17T19:29:57.532Z</v>
       </c>
     </row>
     <row r="5">
